--- a/data/review/gpt-5.4-pro/step-4-review.xlsx
+++ b/data/review/gpt-5.4-pro/step-4-review.xlsx
@@ -430,13 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,6 +458,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>llm_decision</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decision</t>
         </is>
       </c>
@@ -477,7 +483,12 @@
           <t>SC1.pdf</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,7 +506,12 @@
           <t>SC2.pdf</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -513,7 +529,12 @@
           <t>SC3.pdf</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -531,7 +552,12 @@
           <t>SC4.pdf</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,7 +575,12 @@
           <t>SC5.pdf</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -567,7 +598,12 @@
           <t>SC6.pdf</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -585,7 +621,12 @@
           <t>SC7.pdf</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -603,7 +644,12 @@
           <t>SC9.pdf</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -621,7 +667,12 @@
           <t>SC12.pdf</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -639,7 +690,12 @@
           <t>SC14.pdf</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -657,7 +713,12 @@
           <t>SC16.pdf</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -675,7 +736,12 @@
           <t>SC17.pdf</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -693,7 +759,12 @@
           <t>SC18.pdf</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -711,7 +782,12 @@
           <t>SC21.pdf</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -729,7 +805,12 @@
           <t>SC23.pdf</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -747,7 +828,12 @@
           <t>SC24.pdf</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -765,7 +851,12 @@
           <t>SC29.pdf</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -783,7 +874,12 @@
           <t>SC30.pdf</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,7 +897,12 @@
           <t>SC31.pdf</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -819,7 +920,12 @@
           <t>SC34.pdf</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -837,7 +943,12 @@
           <t>SC35.pdf</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -851,7 +962,12 @@
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -869,7 +985,12 @@
           <t>SC41.pdf</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -887,7 +1008,12 @@
           <t>SC43.pdf</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -905,7 +1031,12 @@
           <t>SC44.pdf</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -923,7 +1054,12 @@
           <t>SC45.pdf</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -941,7 +1077,12 @@
           <t>SC46.pdf</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -959,7 +1100,12 @@
           <t>SC47.pdf</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -977,7 +1123,12 @@
           <t>SC48.pdf</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -995,7 +1146,12 @@
           <t>SC52.pdf</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1013,7 +1169,12 @@
           <t>SC54.pdf</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1031,7 +1192,12 @@
           <t>SC56.pdf</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1049,7 +1215,12 @@
           <t>SC58.pdf</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1067,7 +1238,12 @@
           <t>SC63.pdf</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1085,7 +1261,12 @@
           <t>SC65.pdf</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1103,7 +1284,12 @@
           <t>SC67.pdf</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1121,7 +1307,12 @@
           <t>SC68.pdf</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1139,7 +1330,12 @@
           <t>SC69.pdf</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1157,7 +1353,12 @@
           <t>SC70.pdf</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1175,7 +1376,12 @@
           <t>SC72.pdf</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1193,7 +1399,12 @@
           <t>SC74.pdf</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1211,7 +1422,12 @@
           <t>SC75.pdf</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1229,7 +1445,12 @@
           <t>SC78.pdf</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1247,7 +1468,12 @@
           <t>SC79.pdf</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1265,7 +1491,12 @@
           <t>SC82.pdf</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1283,7 +1514,12 @@
           <t>SC83.pdf</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1301,7 +1537,12 @@
           <t>SC85.pdf</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1319,7 +1560,12 @@
           <t>SC89.pdf</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1337,7 +1583,12 @@
           <t>SC92.pdf</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1355,7 +1606,12 @@
           <t>SC95.pdf</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1373,7 +1629,12 @@
           <t>SC96.pdf</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1391,7 +1652,12 @@
           <t>SC97.pdf</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1409,7 +1675,12 @@
           <t>SC98.pdf</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1427,7 +1698,12 @@
           <t>SC103.pdf</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1445,7 +1721,12 @@
           <t>SC107.pdf</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1463,7 +1744,12 @@
           <t>SC111.pdf</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1481,7 +1767,12 @@
           <t>SC112.pdf</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1499,7 +1790,12 @@
           <t>SC115.pdf</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1517,7 +1813,12 @@
           <t>SC116.pdf</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1535,7 +1836,12 @@
           <t>SC117.pdf</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1553,7 +1859,12 @@
           <t>SC122.pdf</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1571,7 +1882,12 @@
           <t>SC127.pdf</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1589,7 +1905,12 @@
           <t>GO1.md</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1607,7 +1928,12 @@
           <t>GO2.md</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1625,7 +1951,12 @@
           <t>GO3.md</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1643,7 +1974,12 @@
           <t>GO5.md</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1661,7 +1997,12 @@
           <t>GO6.md</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1679,7 +2020,12 @@
           <t>GO8.md</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1697,7 +2043,12 @@
           <t>GO9.md</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1715,7 +2066,12 @@
           <t>GO12.md</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1733,7 +2089,12 @@
           <t>GO15.md</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1751,7 +2112,12 @@
           <t>GO16.md</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1769,7 +2135,12 @@
           <t>GO18.md</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1787,7 +2158,12 @@
           <t>GO22.md</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1805,7 +2181,12 @@
           <t>GO23.md</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1823,7 +2204,12 @@
           <t>GO24.md</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1841,7 +2227,12 @@
           <t>GO25.md</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1859,7 +2250,12 @@
           <t>GO26.md</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1877,7 +2273,12 @@
           <t>GO34.md</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1895,7 +2296,12 @@
           <t>GO36.md</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1913,7 +2319,12 @@
           <t>GO40.md</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1931,7 +2342,12 @@
           <t>GO42.md</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1949,7 +2365,12 @@
           <t>GO44.md</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1967,7 +2388,12 @@
           <t>GO47.md</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1985,7 +2411,12 @@
           <t>GO48.md</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2003,7 +2434,12 @@
           <t>GO49.md</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2021,7 +2457,12 @@
           <t>GO51.md</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2039,7 +2480,12 @@
           <t>GO53.md</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2057,7 +2503,12 @@
           <t>GO54.md</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2075,7 +2526,12 @@
           <t>GO58.md</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2093,7 +2549,12 @@
           <t>GO62.md</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2111,7 +2572,12 @@
           <t>GO64.md</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2129,7 +2595,12 @@
           <t>GO77.md</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2147,7 +2618,12 @@
           <t>GO79.md</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2165,7 +2641,12 @@
           <t>GO86.md</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2183,7 +2664,12 @@
           <t>GO88.md</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2201,7 +2687,12 @@
           <t>GO92.md</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2219,7 +2710,12 @@
           <t>GO96.md</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2237,7 +2733,12 @@
           <t>GO98.md</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2255,7 +2756,12 @@
           <t>GH6.md</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2273,7 +2779,12 @@
           <t>GH7.md</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2291,7 +2802,12 @@
           <t>GH8.md</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2309,7 +2825,12 @@
           <t>GH9.md</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2327,7 +2848,12 @@
           <t>GH10.md</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2345,7 +2871,12 @@
           <t>GH12.md</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2363,7 +2894,12 @@
           <t>GH14.md</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2381,7 +2917,12 @@
           <t>GH22.md</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2399,7 +2940,12 @@
           <t>GH24.md</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2417,7 +2963,12 @@
           <t>GH25.md</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2435,7 +2986,12 @@
           <t>GH26.md</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2453,7 +3009,12 @@
           <t>GH27.md</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2471,7 +3032,12 @@
           <t>GH30.md</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2489,7 +3055,12 @@
           <t>GH31.md</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2507,7 +3078,12 @@
           <t>GH33.md</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2525,7 +3101,12 @@
           <t>GH35.md</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2543,7 +3124,12 @@
           <t>GH36.md</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2561,7 +3147,12 @@
           <t>GH38.md</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2579,7 +3170,12 @@
           <t>GH39.md</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2597,7 +3193,12 @@
           <t>GH41.md</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2615,7 +3216,12 @@
           <t>GH42.md</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2633,7 +3239,12 @@
           <t>GH45.md</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2651,7 +3262,12 @@
           <t>GH47.md</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2669,7 +3285,12 @@
           <t>GH48.md</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2687,7 +3308,12 @@
           <t>GH50.md</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2705,7 +3331,12 @@
           <t>GH56.md</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2723,7 +3354,12 @@
           <t>GH60.md</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2741,7 +3377,12 @@
           <t>GH62.md</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2759,7 +3400,12 @@
           <t>GH64.md</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2777,7 +3423,12 @@
           <t>GH65.md</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2795,7 +3446,12 @@
           <t>GH68.md</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2813,7 +3469,12 @@
           <t>GH72.md</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2831,7 +3492,12 @@
           <t>GH73.md</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2849,7 +3515,12 @@
           <t>GH77.md</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2867,7 +3538,12 @@
           <t>GH78.md</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2885,7 +3561,12 @@
           <t>GH79.md</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2903,7 +3584,12 @@
           <t>GH80.md</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2921,7 +3607,12 @@
           <t>GH91.md</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2939,7 +3630,12 @@
           <t>GH93.md</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2957,7 +3653,12 @@
           <t>HF1.pdf</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2975,7 +3676,12 @@
           <t>HF3.pdf</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2993,7 +3699,12 @@
           <t>HF4.pdf</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3011,7 +3722,12 @@
           <t>HF5.pdf</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3029,7 +3745,12 @@
           <t>HF6.pdf</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3047,7 +3768,12 @@
           <t>HF7.pdf</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3065,7 +3791,12 @@
           <t>HF8.pdf</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3083,7 +3814,12 @@
           <t>HF9.pdf</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3101,7 +3837,12 @@
           <t>HF10.pdf</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3119,7 +3860,12 @@
           <t>HF11.pdf</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3137,7 +3883,12 @@
           <t>HF13.pdf</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3155,7 +3906,12 @@
           <t>HF14.pdf</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3173,7 +3929,12 @@
           <t>HF15.pdf</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3191,7 +3952,12 @@
           <t>HF17.pdf</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3209,7 +3975,12 @@
           <t>HF18.pdf</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3227,7 +3998,12 @@
           <t>HF19.pdf</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3245,7 +4021,12 @@
           <t>HF20.pdf</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3263,7 +4044,12 @@
           <t>HF21.pdf</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3281,7 +4067,12 @@
           <t>HF22.pdf</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3299,7 +4090,12 @@
           <t>HF23.pdf</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3317,7 +4113,12 @@
           <t>HF25.pdf</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3335,7 +4136,12 @@
           <t>HF26.pdf</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3353,7 +4159,12 @@
           <t>HF27.pdf</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3371,7 +4182,12 @@
           <t>HF28.pdf</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3389,7 +4205,12 @@
           <t>HF30.pdf</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3407,7 +4228,12 @@
           <t>HF31.pdf</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3425,7 +4251,12 @@
           <t>HF32.pdf</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3443,7 +4274,12 @@
           <t>HF33.pdf</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3461,7 +4297,12 @@
           <t>HF34.pdf</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3475,7 +4316,12 @@
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3493,7 +4339,12 @@
           <t>HF41.pdf</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3511,7 +4362,12 @@
           <t>HF42.pdf</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3529,7 +4385,12 @@
           <t>HF44.pdf</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3547,7 +4408,12 @@
           <t>HF47.pdf</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3565,7 +4431,12 @@
           <t>HF49.pdf</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3583,7 +4454,12 @@
           <t>HF52.pdf</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3601,7 +4477,12 @@
           <t>HF53.pdf</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3619,7 +4500,12 @@
           <t>HF56.pdf</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3637,11 +4523,16 @@
           <t>HF71.pdf</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/review/gpt-5.4-pro/step-4-review.xlsx
+++ b/data/review/gpt-5.4-pro/step-4-review.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,6 +467,11 @@
           <t>decision</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +495,7 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,6 +519,7 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,6 +543,7 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,6 +567,7 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -581,6 +591,7 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +615,7 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -627,6 +639,7 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,6 +663,7 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -673,6 +687,7 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -696,6 +711,7 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -719,6 +735,7 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -742,6 +759,7 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -765,6 +783,7 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -788,6 +807,7 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -811,6 +831,7 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -834,6 +855,7 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,6 +879,7 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -880,6 +903,7 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -903,6 +927,7 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -926,6 +951,7 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -949,6 +975,7 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -968,6 +995,7 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -991,6 +1019,7 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1014,6 +1043,7 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1037,6 +1067,7 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1060,6 +1091,7 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1083,6 +1115,7 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1106,6 +1139,7 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1129,6 +1163,7 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1152,6 +1187,7 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1175,6 +1211,7 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1198,6 +1235,7 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1221,6 +1259,7 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1244,6 +1283,7 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1267,6 +1307,7 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1290,6 +1331,7 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1313,6 +1355,7 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1336,6 +1379,7 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1359,6 +1403,7 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1382,6 +1427,7 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1405,6 +1451,7 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1428,6 +1475,7 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1451,6 +1499,7 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1474,6 +1523,7 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1497,6 +1547,7 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1520,6 +1571,7 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1543,6 +1595,7 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1566,6 +1619,7 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1589,6 +1643,7 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1612,6 +1667,7 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1635,6 +1691,7 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1658,6 +1715,7 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1681,6 +1739,7 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1704,6 +1763,7 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1727,6 +1787,7 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1750,6 +1811,7 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1773,6 +1835,7 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1796,6 +1859,7 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1819,6 +1883,7 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1842,6 +1907,7 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1865,6 +1931,7 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1888,6 +1955,7 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1911,6 +1979,7 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1934,6 +2003,7 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1957,6 +2027,7 @@
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1980,6 +2051,7 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2003,6 +2075,7 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2026,6 +2099,7 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2049,6 +2123,7 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2072,6 +2147,7 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2095,6 +2171,7 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2118,6 +2195,7 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2141,6 +2219,7 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2164,6 +2243,7 @@
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2187,6 +2267,7 @@
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2210,6 +2291,7 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2233,6 +2315,7 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2256,6 +2339,7 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2279,6 +2363,7 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2302,6 +2387,7 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2325,6 +2411,7 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2348,6 +2435,7 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2371,6 +2459,7 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2394,6 +2483,7 @@
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2417,6 +2507,7 @@
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2440,6 +2531,7 @@
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2463,6 +2555,7 @@
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2486,6 +2579,7 @@
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2509,6 +2603,7 @@
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2532,6 +2627,7 @@
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2555,6 +2651,7 @@
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2578,6 +2675,7 @@
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2601,6 +2699,7 @@
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2624,6 +2723,7 @@
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2647,6 +2747,7 @@
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2670,6 +2771,7 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2693,6 +2795,7 @@
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2716,6 +2819,7 @@
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2739,6 +2843,7 @@
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2762,6 +2867,7 @@
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2785,6 +2891,7 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2808,6 +2915,7 @@
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2831,6 +2939,7 @@
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2854,6 +2963,7 @@
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2877,6 +2987,7 @@
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2900,6 +3011,7 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2923,6 +3035,7 @@
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2946,6 +3059,7 @@
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2969,6 +3083,7 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2992,6 +3107,7 @@
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3015,6 +3131,7 @@
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3038,6 +3155,7 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3061,6 +3179,7 @@
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3084,6 +3203,7 @@
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3107,6 +3227,7 @@
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3130,6 +3251,7 @@
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3153,6 +3275,7 @@
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3176,6 +3299,7 @@
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3199,6 +3323,7 @@
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3222,6 +3347,7 @@
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3245,6 +3371,7 @@
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3268,6 +3395,7 @@
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3291,6 +3419,7 @@
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3314,6 +3443,7 @@
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3337,6 +3467,7 @@
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3360,6 +3491,7 @@
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3383,6 +3515,7 @@
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3406,6 +3539,7 @@
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3429,6 +3563,7 @@
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3452,6 +3587,7 @@
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3475,6 +3611,7 @@
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3498,6 +3635,7 @@
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3521,6 +3659,7 @@
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3544,6 +3683,7 @@
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3567,6 +3707,7 @@
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3590,6 +3731,7 @@
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3613,6 +3755,7 @@
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3636,6 +3779,7 @@
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3659,6 +3803,7 @@
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3682,6 +3827,7 @@
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3705,6 +3851,7 @@
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3728,6 +3875,7 @@
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3751,6 +3899,7 @@
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3774,6 +3923,7 @@
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3797,6 +3947,7 @@
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3820,6 +3971,7 @@
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3843,6 +3995,7 @@
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3866,6 +4019,7 @@
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3889,6 +4043,7 @@
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3912,6 +4067,7 @@
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3935,6 +4091,7 @@
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3958,6 +4115,7 @@
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3981,6 +4139,7 @@
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4004,6 +4163,7 @@
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4027,6 +4187,7 @@
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4050,6 +4211,7 @@
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4073,6 +4235,7 @@
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4096,6 +4259,7 @@
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4119,6 +4283,7 @@
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4142,6 +4307,7 @@
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4165,6 +4331,7 @@
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4188,6 +4355,7 @@
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4211,6 +4379,7 @@
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4234,6 +4403,7 @@
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4257,6 +4427,7 @@
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4280,6 +4451,7 @@
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4303,6 +4475,7 @@
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4322,6 +4495,7 @@
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4345,6 +4519,7 @@
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4368,6 +4543,7 @@
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4391,6 +4567,7 @@
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4414,6 +4591,7 @@
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4437,6 +4615,7 @@
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4460,6 +4639,7 @@
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4483,6 +4663,7 @@
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4506,6 +4687,7 @@
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4529,11 +4711,15 @@
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="E2:E178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Reviewer A,Reviewer B"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
